--- a/output/loan_data.xlsx
+++ b/output/loan_data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4842,6 +4842,50 @@
       <c r="N100" t="inlineStr">
         <is>
           <t>5.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>121Y006</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1.3.3.2.1. 예금은행 대출금리(신규취급액 기준)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BECBLA03051</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>일반신용대출 2)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>연리%</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>6.33</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9287,6 +9331,50 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>121Y006</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1.3.3.2.1. 예금은행 대출금리(신규취급액 기준)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BECBLA0302</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>주택담보대출</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>연리%</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/loan_data.xlsx
+++ b/output/loan_data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,12 +524,12 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>201805</t>
+          <t>201806</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.57</t>
         </is>
       </c>
     </row>
@@ -568,12 +568,12 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>201806</t>
+          <t>201807</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.56</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>201807</t>
+          <t>201808</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.47</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>201808</t>
+          <t>201809</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.39</t>
         </is>
       </c>
     </row>
@@ -700,12 +700,12 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>201809</t>
+          <t>201810</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.45</t>
         </is>
       </c>
     </row>
@@ -744,12 +744,12 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>201810</t>
+          <t>201811</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.56</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>201811</t>
+          <t>201812</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.64</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>201812</t>
+          <t>201901</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.57</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>201901</t>
+          <t>201902</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.49</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>201902</t>
+          <t>201903</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.63</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>201903</t>
+          <t>201904</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.54</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>201904</t>
+          <t>201905</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>201905</t>
+          <t>201906</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.23</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>201906</t>
+          <t>201907</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>3.96</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>201907</t>
+          <t>201908</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.63</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>201908</t>
+          <t>201909</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.86</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>201909</t>
+          <t>201910</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.9</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>201910</t>
+          <t>201911</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1316,12 +1316,12 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>201911</t>
+          <t>201912</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.87</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>201912</t>
+          <t>202001</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.83</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>202001</t>
+          <t>202002</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>3.7</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>202002</t>
+          <t>202003</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.49</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>202003</t>
+          <t>202004</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.5</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>202004</t>
+          <t>202005</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.33</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>202005</t>
+          <t>202006</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.93</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>202006</t>
+          <t>202007</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.92</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>202007</t>
+          <t>202008</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.86</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>202008</t>
+          <t>202009</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.89</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>202009</t>
+          <t>202010</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>3.15</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>202010</t>
+          <t>202011</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>202011</t>
+          <t>202012</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.5</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1888,12 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>202012</t>
+          <t>202101</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
     </row>
@@ -1932,12 +1932,12 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>202102</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.61</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>202102</t>
+          <t>202103</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.7</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2020,12 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>202103</t>
+          <t>202104</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.65</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>202104</t>
+          <t>202105</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.69</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2108,12 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>202105</t>
+          <t>202106</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2152,12 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>202106</t>
+          <t>202107</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.86</t>
         </is>
       </c>
     </row>
@@ -2196,12 +2196,12 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>202107</t>
+          <t>202108</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.97</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>202108</t>
+          <t>202109</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.15</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2284,12 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>202109</t>
+          <t>202110</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.62</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>202110</t>
+          <t>202111</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>5.16</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>202111</t>
+          <t>202112</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2416,12 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>202112</t>
+          <t>202201</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.28</t>
         </is>
       </c>
     </row>
@@ -2460,12 +2460,12 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>202201</t>
+          <t>202202</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.33</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>202202</t>
+          <t>202203</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>5.46</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>202203</t>
+          <t>202204</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.62</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>202204</t>
+          <t>202205</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.78</t>
         </is>
       </c>
     </row>
@@ -2636,12 +2636,12 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>202205</t>
+          <t>202206</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>202206</t>
+          <t>202207</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.91</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2724,12 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>202207</t>
+          <t>202208</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>6.24</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>202208</t>
+          <t>202209</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.62</t>
         </is>
       </c>
     </row>
@@ -2812,12 +2812,12 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>202209</t>
+          <t>202210</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>7.22</t>
         </is>
       </c>
     </row>
@@ -2856,12 +2856,12 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>202210</t>
+          <t>202211</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>7.85</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>202211</t>
+          <t>202212</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.97</t>
         </is>
       </c>
     </row>
@@ -2944,12 +2944,12 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>202212</t>
+          <t>202301</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>7.21</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>202301</t>
+          <t>202302</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>6.55</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>202302</t>
+          <t>202303</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.44</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3076,12 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>202303</t>
+          <t>202304</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.3</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>202304</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.56</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3164,12 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>202305</t>
+          <t>202306</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.47</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3208,12 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>202306</t>
+          <t>202307</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.52</t>
         </is>
       </c>
     </row>
@@ -3252,12 +3252,12 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>202307</t>
+          <t>202308</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.53</t>
         </is>
       </c>
     </row>
@@ -3296,12 +3296,12 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>202308</t>
+          <t>202309</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>6.59</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>202309</t>
+          <t>202310</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>6.81</t>
         </is>
       </c>
     </row>
@@ -3384,12 +3384,12 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>202310</t>
+          <t>202311</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.85</t>
         </is>
       </c>
     </row>
@@ -3428,12 +3428,12 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>202311</t>
+          <t>202312</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.58</t>
         </is>
       </c>
     </row>
@@ -3472,12 +3472,12 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>202312</t>
+          <t>202401</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.38</t>
         </is>
       </c>
     </row>
@@ -3516,12 +3516,12 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>202401</t>
+          <t>202402</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.29</t>
         </is>
       </c>
     </row>
@@ -3560,12 +3560,12 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>202402</t>
+          <t>202403</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.14</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3604,12 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>202403</t>
+          <t>202404</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -3648,12 +3648,12 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>202404</t>
+          <t>202405</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.11</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>202405</t>
+          <t>202406</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -3736,12 +3736,12 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>202406</t>
+          <t>202407</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.78</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3780,12 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>202407</t>
+          <t>202408</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.65</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>202408</t>
+          <t>202409</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.87</t>
         </is>
       </c>
     </row>
@@ -3868,12 +3868,12 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>202409</t>
+          <t>202410</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.86</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>202410</t>
+          <t>202411</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>6.17</t>
         </is>
       </c>
     </row>
@@ -3956,12 +3956,12 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>202411</t>
+          <t>202412</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.15</t>
         </is>
       </c>
     </row>
@@ -4000,12 +4000,12 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>202412</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.58</t>
         </is>
       </c>
     </row>
@@ -4044,12 +4044,12 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.5</t>
         </is>
       </c>
     </row>
@@ -4088,12 +4088,12 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.48</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.28</t>
         </is>
       </c>
     </row>
@@ -4176,12 +4176,12 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.21</t>
         </is>
       </c>
     </row>
@@ -4220,12 +4220,12 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>5.03</t>
         </is>
       </c>
     </row>
@@ -4264,12 +4264,12 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.34</t>
         </is>
       </c>
     </row>
@@ -4308,12 +4308,12 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.41</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.31</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.19</t>
         </is>
       </c>
     </row>
@@ -4440,12 +4440,12 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>5.46</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.87</t>
         </is>
       </c>
     </row>
@@ -4528,12 +4528,12 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.55</t>
         </is>
       </c>
     </row>
@@ -4572,12 +4572,12 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.53</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.57</t>
         </is>
       </c>
     </row>
@@ -4660,12 +4660,12 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.63</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4704,12 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.49</t>
         </is>
       </c>
     </row>
@@ -4748,12 +4748,12 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.72</t>
         </is>
       </c>
     </row>
@@ -4792,12 +4792,12 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.97</t>
         </is>
       </c>
     </row>
@@ -4836,54 +4836,10 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
-        <is>
-          <t>5.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>121Y006</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>1.3.3.2.1. 예금은행 대출금리(신규취급액 기준)</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>BECBLA03051</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>일반신용대출 2)</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>연리%</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>202608</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
         <is>
           <t>6.33</t>
         </is>
@@ -4900,7 +4856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5010,12 +4966,12 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>201805</t>
+          <t>201806</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.46</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5010,12 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>201806</t>
+          <t>201807</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.44</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5054,12 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>201807</t>
+          <t>201808</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.36</t>
         </is>
       </c>
     </row>
@@ -5142,12 +5098,12 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>201808</t>
+          <t>201809</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.29</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5142,12 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>201809</t>
+          <t>201810</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.31</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5186,12 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>201810</t>
+          <t>201811</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.28</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5230,12 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>201811</t>
+          <t>201812</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.19</t>
         </is>
       </c>
     </row>
@@ -5318,12 +5274,12 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>201812</t>
+          <t>201901</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -5362,12 +5318,12 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>201901</t>
+          <t>201902</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.08</t>
         </is>
       </c>
     </row>
@@ -5406,12 +5362,12 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>201902</t>
+          <t>201903</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -5450,12 +5406,12 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>201903</t>
+          <t>201904</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.98</t>
         </is>
       </c>
     </row>
@@ -5494,12 +5450,12 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>201904</t>
+          <t>201905</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.93</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5494,12 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>201905</t>
+          <t>201906</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.74</t>
         </is>
       </c>
     </row>
@@ -5582,12 +5538,12 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>201906</t>
+          <t>201907</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.64</t>
         </is>
       </c>
     </row>
@@ -5626,12 +5582,12 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>201907</t>
+          <t>201908</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.47</t>
         </is>
       </c>
     </row>
@@ -5670,12 +5626,12 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>201908</t>
+          <t>201909</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.51</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5670,12 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>201909</t>
+          <t>201910</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.5</t>
         </is>
       </c>
     </row>
@@ -5758,12 +5714,12 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>201910</t>
+          <t>201911</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5758,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>201911</t>
+          <t>201912</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -5846,12 +5802,12 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>201912</t>
+          <t>202001</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.51</t>
         </is>
       </c>
     </row>
@@ -5890,12 +5846,12 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>202001</t>
+          <t>202002</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.52</t>
         </is>
       </c>
     </row>
@@ -5934,12 +5890,12 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>202002</t>
+          <t>202003</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
     </row>
@@ -5978,12 +5934,12 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>202003</t>
+          <t>202004</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.58</t>
         </is>
       </c>
     </row>
@@ -6022,12 +5978,12 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>202004</t>
+          <t>202005</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.52</t>
         </is>
       </c>
     </row>
@@ -6066,12 +6022,12 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>202005</t>
+          <t>202006</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.49</t>
         </is>
       </c>
     </row>
@@ -6110,12 +6066,12 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>202006</t>
+          <t>202007</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
@@ -6154,12 +6110,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>202007</t>
+          <t>202008</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.39</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6154,12 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>202008</t>
+          <t>202009</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.44</t>
         </is>
       </c>
     </row>
@@ -6242,12 +6198,12 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>202009</t>
+          <t>202010</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.47</t>
         </is>
       </c>
     </row>
@@ -6286,12 +6242,12 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>202010</t>
+          <t>202011</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.56</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6286,12 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>202011</t>
+          <t>202012</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.59</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6330,12 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>202012</t>
+          <t>202101</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6374,12 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>202102</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.66</t>
         </is>
       </c>
     </row>
@@ -6462,12 +6418,12 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>202102</t>
+          <t>202103</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.73</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6462,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>202103</t>
+          <t>202104</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -6550,12 +6506,12 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>202104</t>
+          <t>202105</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.69</t>
         </is>
       </c>
     </row>
@@ -6594,12 +6550,12 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>202105</t>
+          <t>202106</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.74</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6594,12 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>202106</t>
+          <t>202107</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.81</t>
         </is>
       </c>
     </row>
@@ -6682,12 +6638,12 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>202107</t>
+          <t>202108</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
@@ -6726,12 +6682,12 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>202108</t>
+          <t>202109</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6726,12 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>202109</t>
+          <t>202110</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.26</t>
         </is>
       </c>
     </row>
@@ -6814,12 +6770,12 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>202110</t>
+          <t>202111</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.51</t>
         </is>
       </c>
     </row>
@@ -6858,12 +6814,12 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>202111</t>
+          <t>202112</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
     </row>
@@ -6902,12 +6858,12 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>202112</t>
+          <t>202201</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.85</t>
         </is>
       </c>
     </row>
@@ -6946,12 +6902,12 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>202201</t>
+          <t>202202</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.88</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6946,12 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>202202</t>
+          <t>202203</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.84</t>
         </is>
       </c>
     </row>
@@ -7034,12 +6990,12 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>202203</t>
+          <t>202204</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.9</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7034,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>202204</t>
+          <t>202205</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7122,12 +7078,12 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>202205</t>
+          <t>202206</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -7166,12 +7122,12 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>202206</t>
+          <t>202207</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.16</t>
         </is>
       </c>
     </row>
@@ -7210,12 +7166,12 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>202207</t>
+          <t>202208</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.35</t>
         </is>
       </c>
     </row>
@@ -7254,12 +7210,12 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>202208</t>
+          <t>202209</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.79</t>
         </is>
       </c>
     </row>
@@ -7298,12 +7254,12 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>202209</t>
+          <t>202210</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.82</t>
         </is>
       </c>
     </row>
@@ -7342,12 +7298,12 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>202210</t>
+          <t>202211</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.74</t>
         </is>
       </c>
     </row>
@@ -7386,12 +7342,12 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>202211</t>
+          <t>202212</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.63</t>
         </is>
       </c>
     </row>
@@ -7430,12 +7386,12 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>202212</t>
+          <t>202301</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.58</t>
         </is>
       </c>
     </row>
@@ -7474,12 +7430,12 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>202301</t>
+          <t>202302</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.56</t>
         </is>
       </c>
     </row>
@@ -7518,12 +7474,12 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>202302</t>
+          <t>202303</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
@@ -7562,12 +7518,12 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>202303</t>
+          <t>202304</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.24</t>
         </is>
       </c>
     </row>
@@ -7606,12 +7562,12 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>202304</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.21</t>
         </is>
       </c>
     </row>
@@ -7650,12 +7606,12 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>202305</t>
+          <t>202306</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.26</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7650,12 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>202306</t>
+          <t>202307</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.28</t>
         </is>
       </c>
     </row>
@@ -7738,12 +7694,12 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>202307</t>
+          <t>202308</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.31</t>
         </is>
       </c>
     </row>
@@ -7782,12 +7738,12 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>202308</t>
+          <t>202309</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.35</t>
         </is>
       </c>
     </row>
@@ -7826,12 +7782,12 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>202309</t>
+          <t>202310</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.56</t>
         </is>
       </c>
     </row>
@@ -7870,12 +7826,12 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>202310</t>
+          <t>202311</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.48</t>
         </is>
       </c>
     </row>
@@ -7914,12 +7870,12 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>202311</t>
+          <t>202312</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.16</t>
         </is>
       </c>
     </row>
@@ -7958,12 +7914,12 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>202312</t>
+          <t>202401</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.99</t>
         </is>
       </c>
     </row>
@@ -8002,12 +7958,12 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>202401</t>
+          <t>202402</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.96</t>
         </is>
       </c>
     </row>
@@ -8046,12 +8002,12 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>202402</t>
+          <t>202403</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.94</t>
         </is>
       </c>
     </row>
@@ -8090,12 +8046,12 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>202403</t>
+          <t>202404</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.93</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8090,12 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>202404</t>
+          <t>202405</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.91</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8134,12 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>202405</t>
+          <t>202406</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.71</t>
         </is>
       </c>
     </row>
@@ -8222,12 +8178,12 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>202406</t>
+          <t>202407</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.5</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8222,12 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>202407</t>
+          <t>202408</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.51</t>
         </is>
       </c>
     </row>
@@ -8310,12 +8266,12 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>202408</t>
+          <t>202409</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.74</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8310,12 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>202409</t>
+          <t>202410</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -8398,12 +8354,12 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>202410</t>
+          <t>202411</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.3</t>
         </is>
       </c>
     </row>
@@ -8442,12 +8398,12 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>202411</t>
+          <t>202412</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.25</t>
         </is>
       </c>
     </row>
@@ -8486,12 +8442,12 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>202412</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.27</t>
         </is>
       </c>
     </row>
@@ -8530,12 +8486,12 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.23</t>
         </is>
       </c>
     </row>
@@ -8574,12 +8530,12 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.17</t>
         </is>
       </c>
     </row>
@@ -8618,12 +8574,12 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.98</t>
         </is>
       </c>
     </row>
@@ -8662,12 +8618,12 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.87</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8662,12 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.93</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8706,12 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.96</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8750,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -8838,7 +8794,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -8882,12 +8838,12 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.98</t>
         </is>
       </c>
     </row>
@@ -8926,12 +8882,12 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.17</t>
         </is>
       </c>
     </row>
@@ -8970,12 +8926,12 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.23</t>
         </is>
       </c>
     </row>
@@ -9014,12 +8970,12 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.29</t>
         </is>
       </c>
     </row>
@@ -9058,12 +9014,12 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.32</t>
         </is>
       </c>
     </row>
@@ -9102,12 +9058,12 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.34</t>
         </is>
       </c>
     </row>
@@ -9146,12 +9102,12 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.31</t>
         </is>
       </c>
     </row>
@@ -9190,12 +9146,12 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
     </row>
@@ -9234,12 +9190,12 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.36</t>
         </is>
       </c>
     </row>
@@ -9278,12 +9234,12 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.48</t>
         </is>
       </c>
     </row>
@@ -9322,54 +9278,10 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
-        <is>
-          <t>4.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>121Y006</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>1.3.3.2.1. 예금은행 대출금리(신규취급액 기준)</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>BECBLA0302</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>주택담보대출</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>연리%</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>202608</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
         <is>
           <t>4.66</t>
         </is>

--- a/output/loan_data.xlsx
+++ b/output/loan_data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4842,6 +4842,50 @@
       <c r="N100" t="inlineStr">
         <is>
           <t>6.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>121Y006</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1.3.3.2.1. 예금은행 대출금리(신규취급액 기준)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BECBLA03051</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>일반신용대출 2)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>연리%</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>6.49</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9287,6 +9331,50 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>121Y006</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1.3.3.2.1. 예금은행 대출금리(신규취급액 기준)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BECBLA0302</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>주택담보대출</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>연리%</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
